--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1268,6 +1268,109 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113453283</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79217</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kullemyr, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>330442</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6532245</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,6 +1371,427 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113460667</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79144</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>515</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blylav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pectenia plumbea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kullemyr (Kullemyr), Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>330458</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6532244</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113460598</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79184</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kullemyr (Kullemyr), Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>330443</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6532276</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113460482</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79144</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>515</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blylav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pectenia plumbea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kullemyr (Kullemyr), Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>330443</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6532276</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113453290</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79144</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>515</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blylav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pectenia plumbea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kullemyr, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>330442</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6532245</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1373,7 +1373,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113460667</v>
+        <v>113460482</v>
       </c>
       <c r="B8" t="n">
         <v>79144</v>
@@ -1407,22 +1407,20 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330458</v>
+        <v>330443</v>
       </c>
       <c r="R8" t="n">
-        <v>6532244</v>
+        <v>6532276</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,7 +1458,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1472,17 +1469,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Oskar Karlsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113460598</v>
+        <v>113460667</v>
       </c>
       <c r="B9" t="n">
-        <v>79184</v>
+        <v>79144</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,25 +1488,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>515</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330443</v>
+        <v>330458</v>
       </c>
       <c r="R9" t="n">
-        <v>6532276</v>
+        <v>6532244</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1585,7 +1582,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113460482</v>
+        <v>113453290</v>
       </c>
       <c r="B10" t="n">
         <v>79144</v>
@@ -1619,17 +1616,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullemyr (Kullemyr), Dls</t>
+          <t>Kullemyr, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330443</v>
+        <v>330442</v>
       </c>
       <c r="R10" t="n">
-        <v>6532276</v>
+        <v>6532245</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,6 +1669,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,17 +1681,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113453290</v>
+        <v>113460598</v>
       </c>
       <c r="B11" t="n">
-        <v>79144</v>
+        <v>79184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,25 +1700,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>515</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,17 +1727,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullemyr, Dls</t>
+          <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330442</v>
+        <v>330443</v>
       </c>
       <c r="R11" t="n">
-        <v>6532245</v>
+        <v>6532276</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1273,7 +1273,7 @@
         <v>113453283</v>
       </c>
       <c r="B7" t="n">
-        <v>79217</v>
+        <v>79229</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>113460482</v>
       </c>
       <c r="B8" t="n">
-        <v>79144</v>
+        <v>79156</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113460667</v>
+        <v>113453290</v>
       </c>
       <c r="B9" t="n">
-        <v>79144</v>
+        <v>79156</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,17 +1515,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullemyr (Kullemyr), Dls</t>
+          <t>Kullemyr, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330458</v>
+        <v>330442</v>
       </c>
       <c r="R9" t="n">
-        <v>6532244</v>
+        <v>6532245</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113453290</v>
+        <v>113460598</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>79196</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,25 +1594,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>515</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,17 +1621,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullemyr, Dls</t>
+          <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330442</v>
+        <v>330443</v>
       </c>
       <c r="R10" t="n">
-        <v>6532245</v>
+        <v>6532276</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113460598</v>
+        <v>113460667</v>
       </c>
       <c r="B11" t="n">
-        <v>79184</v>
+        <v>79156</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,25 +1700,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>515</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330443</v>
+        <v>330458</v>
       </c>
       <c r="R11" t="n">
-        <v>6532276</v>
+        <v>6532244</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1373,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113460482</v>
+        <v>113460598</v>
       </c>
       <c r="B8" t="n">
-        <v>79156</v>
+        <v>79196</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,29 +1385,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>515</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kullemyr (Kullemyr), Dls</t>
@@ -1420,7 +1422,7 @@
         <v>6532276</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,6 +1460,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1472,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1582,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113460598</v>
+        <v>113460482</v>
       </c>
       <c r="B10" t="n">
-        <v>79196</v>
+        <v>79156</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,31 +1597,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>515</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kullemyr (Kullemyr), Dls</t>
@@ -1631,7 +1632,7 @@
         <v>6532276</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,7 +1670,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Oskar Karlsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1273,7 +1273,7 @@
         <v>113453283</v>
       </c>
       <c r="B7" t="n">
-        <v>79229</v>
+        <v>79251</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>113460598</v>
       </c>
       <c r="B8" t="n">
-        <v>79196</v>
+        <v>79218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113453290</v>
+        <v>113460482</v>
       </c>
       <c r="B9" t="n">
-        <v>79156</v>
+        <v>79178</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,19 +1513,17 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullemyr, Dls</t>
+          <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330442</v>
+        <v>330443</v>
       </c>
       <c r="R9" t="n">
-        <v>6532245</v>
+        <v>6532276</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1566,7 +1564,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1578,17 +1575,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Oskar Karlsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113460482</v>
+        <v>113453290</v>
       </c>
       <c r="B10" t="n">
-        <v>79156</v>
+        <v>79178</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,17 +1616,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullemyr (Kullemyr), Dls</t>
+          <t>Kullemyr, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330443</v>
+        <v>330442</v>
       </c>
       <c r="R10" t="n">
-        <v>6532276</v>
+        <v>6532245</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,6 +1669,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
         <v>113460667</v>
       </c>
       <c r="B11" t="n">
-        <v>79156</v>
+        <v>79178</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1273,7 +1273,7 @@
         <v>113453283</v>
       </c>
       <c r="B7" t="n">
-        <v>79251</v>
+        <v>79255</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>113460598</v>
       </c>
       <c r="B8" t="n">
-        <v>79218</v>
+        <v>79222</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>113460482</v>
       </c>
       <c r="B9" t="n">
-        <v>79178</v>
+        <v>79182</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>113453290</v>
       </c>
       <c r="B10" t="n">
-        <v>79178</v>
+        <v>79182</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>113460667</v>
       </c>
       <c r="B11" t="n">
-        <v>79178</v>
+        <v>79182</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1373,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113460598</v>
+        <v>113460667</v>
       </c>
       <c r="B8" t="n">
-        <v>79222</v>
+        <v>79188</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,25 +1385,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>515</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330443</v>
+        <v>330458</v>
       </c>
       <c r="R8" t="n">
-        <v>6532276</v>
+        <v>6532244</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113460482</v>
+        <v>113460598</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79228</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,29 +1491,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>515</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kullemyr (Kullemyr), Dls</t>
@@ -1526,7 +1528,7 @@
         <v>6532276</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,6 +1566,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,17 +1578,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113453290</v>
+        <v>113460482</v>
       </c>
       <c r="B10" t="n">
-        <v>79182</v>
+        <v>79188</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,19 +1619,17 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullemyr, Dls</t>
+          <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330442</v>
+        <v>330443</v>
       </c>
       <c r="R10" t="n">
-        <v>6532245</v>
+        <v>6532276</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1670,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,17 +1681,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Oskar Karlsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113460667</v>
+        <v>113453290</v>
       </c>
       <c r="B11" t="n">
-        <v>79182</v>
+        <v>79188</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,17 +1727,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullemyr (Kullemyr), Dls</t>
+          <t>Kullemyr, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330458</v>
+        <v>330442</v>
       </c>
       <c r="R11" t="n">
-        <v>6532244</v>
+        <v>6532245</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1273,7 +1273,7 @@
         <v>113453283</v>
       </c>
       <c r="B7" t="n">
-        <v>79255</v>
+        <v>79261</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1373,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113460667</v>
+        <v>113460598</v>
       </c>
       <c r="B8" t="n">
-        <v>79188</v>
+        <v>79228</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,25 +1385,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>515</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330458</v>
+        <v>330443</v>
       </c>
       <c r="R8" t="n">
-        <v>6532244</v>
+        <v>6532276</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113460598</v>
+        <v>113460482</v>
       </c>
       <c r="B9" t="n">
-        <v>79228</v>
+        <v>79188</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,31 +1491,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>515</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kullemyr (Kullemyr), Dls</t>
@@ -1528,7 +1526,7 @@
         <v>6532276</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,7 +1564,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1578,14 +1575,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Oskar Karlsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113460482</v>
+        <v>113453290</v>
       </c>
       <c r="B10" t="n">
         <v>79188</v>
@@ -1619,17 +1616,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullemyr (Kullemyr), Dls</t>
+          <t>Kullemyr, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330443</v>
+        <v>330442</v>
       </c>
       <c r="R10" t="n">
-        <v>6532276</v>
+        <v>6532245</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,6 +1669,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,14 +1681,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113453290</v>
+        <v>113460667</v>
       </c>
       <c r="B11" t="n">
         <v>79188</v>
@@ -1727,17 +1727,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullemyr, Dls</t>
+          <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330442</v>
+        <v>330458</v>
       </c>
       <c r="R11" t="n">
-        <v>6532245</v>
+        <v>6532244</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1273,7 +1273,7 @@
         <v>113453283</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79268</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>113460598</v>
       </c>
       <c r="B8" t="n">
-        <v>79228</v>
+        <v>79235</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113460482</v>
+        <v>113460667</v>
       </c>
       <c r="B9" t="n">
-        <v>79188</v>
+        <v>79195</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,20 +1513,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330443</v>
+        <v>330458</v>
       </c>
       <c r="R9" t="n">
-        <v>6532276</v>
+        <v>6532244</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,6 +1566,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,17 +1578,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113453290</v>
+        <v>113460482</v>
       </c>
       <c r="B10" t="n">
-        <v>79188</v>
+        <v>79195</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,19 +1619,17 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullemyr, Dls</t>
+          <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330442</v>
+        <v>330443</v>
       </c>
       <c r="R10" t="n">
-        <v>6532245</v>
+        <v>6532276</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1670,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,17 +1681,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Oskar Karlsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113460667</v>
+        <v>113453290</v>
       </c>
       <c r="B11" t="n">
-        <v>79188</v>
+        <v>79195</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,17 +1727,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullemyr (Kullemyr), Dls</t>
+          <t>Kullemyr, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330458</v>
+        <v>330442</v>
       </c>
       <c r="R11" t="n">
-        <v>6532244</v>
+        <v>6532245</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1273,7 +1273,7 @@
         <v>113453283</v>
       </c>
       <c r="B7" t="n">
-        <v>79268</v>
+        <v>79270</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113460598</v>
+        <v>113460667</v>
       </c>
       <c r="B8" t="n">
-        <v>79235</v>
+        <v>79197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,25 +1385,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>515</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330443</v>
+        <v>330458</v>
       </c>
       <c r="R8" t="n">
-        <v>6532276</v>
+        <v>6532244</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113460667</v>
+        <v>113460598</v>
       </c>
       <c r="B9" t="n">
-        <v>79195</v>
+        <v>79237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,25 +1491,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>515</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330458</v>
+        <v>330443</v>
       </c>
       <c r="R9" t="n">
-        <v>6532244</v>
+        <v>6532276</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1588,7 +1588,7 @@
         <v>113460482</v>
       </c>
       <c r="B10" t="n">
-        <v>79195</v>
+        <v>79197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>113453290</v>
       </c>
       <c r="B11" t="n">
-        <v>79195</v>
+        <v>79197</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1273,7 +1273,7 @@
         <v>113453283</v>
       </c>
       <c r="B7" t="n">
-        <v>79270</v>
+        <v>79298</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>113460667</v>
       </c>
       <c r="B8" t="n">
-        <v>79197</v>
+        <v>79225</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113460598</v>
+        <v>113453290</v>
       </c>
       <c r="B9" t="n">
-        <v>79237</v>
+        <v>79225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,25 +1491,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>515</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,17 +1518,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullemyr (Kullemyr), Dls</t>
+          <t>Kullemyr, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330443</v>
+        <v>330442</v>
       </c>
       <c r="R9" t="n">
-        <v>6532276</v>
+        <v>6532245</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113460482</v>
+        <v>113460598</v>
       </c>
       <c r="B10" t="n">
-        <v>79197</v>
+        <v>79265</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,29 +1597,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>515</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kullemyr (Kullemyr), Dls</t>
@@ -1632,7 +1634,7 @@
         <v>6532276</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,6 +1672,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,17 +1684,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113453290</v>
+        <v>113460482</v>
       </c>
       <c r="B11" t="n">
-        <v>79197</v>
+        <v>79225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,19 +1725,17 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullemyr, Dls</t>
+          <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330442</v>
+        <v>330443</v>
       </c>
       <c r="R11" t="n">
-        <v>6532245</v>
+        <v>6532276</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1775,7 +1776,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Oskar Karlsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113453290</v>
+        <v>113460598</v>
       </c>
       <c r="B9" t="n">
-        <v>79225</v>
+        <v>79265</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,25 +1491,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>515</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,17 +1518,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullemyr, Dls</t>
+          <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330442</v>
+        <v>330443</v>
       </c>
       <c r="R9" t="n">
-        <v>6532245</v>
+        <v>6532276</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113460598</v>
+        <v>113453290</v>
       </c>
       <c r="B10" t="n">
-        <v>79265</v>
+        <v>79225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,25 +1597,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>515</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,17 +1624,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullemyr (Kullemyr), Dls</t>
+          <t>Kullemyr, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330443</v>
+        <v>330442</v>
       </c>
       <c r="R10" t="n">
-        <v>6532276</v>
+        <v>6532245</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1373,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113460667</v>
+        <v>113460598</v>
       </c>
       <c r="B8" t="n">
-        <v>79225</v>
+        <v>79265</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,25 +1385,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>515</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330458</v>
+        <v>330443</v>
       </c>
       <c r="R8" t="n">
-        <v>6532244</v>
+        <v>6532276</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113460598</v>
+        <v>113453290</v>
       </c>
       <c r="B9" t="n">
-        <v>79265</v>
+        <v>79225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,25 +1491,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>515</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,17 +1518,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullemyr (Kullemyr), Dls</t>
+          <t>Kullemyr, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330443</v>
+        <v>330442</v>
       </c>
       <c r="R9" t="n">
-        <v>6532276</v>
+        <v>6532245</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113453290</v>
+        <v>113460667</v>
       </c>
       <c r="B10" t="n">
         <v>79225</v>
@@ -1624,17 +1624,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullemyr, Dls</t>
+          <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330442</v>
+        <v>330458</v>
       </c>
       <c r="R10" t="n">
-        <v>6532245</v>
+        <v>6532244</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113453290</v>
+        <v>113460667</v>
       </c>
       <c r="B9" t="n">
         <v>79225</v>
@@ -1518,17 +1518,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullemyr, Dls</t>
+          <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330442</v>
+        <v>330458</v>
       </c>
       <c r="R9" t="n">
-        <v>6532245</v>
+        <v>6532244</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113460667</v>
+        <v>113460482</v>
       </c>
       <c r="B10" t="n">
         <v>79225</v>
@@ -1619,22 +1619,20 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kullemyr (Kullemyr), Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330458</v>
+        <v>330443</v>
       </c>
       <c r="R10" t="n">
-        <v>6532244</v>
+        <v>6532276</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1672,7 +1670,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1684,14 +1681,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Oskar Karlsson</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113460482</v>
+        <v>113453290</v>
       </c>
       <c r="B11" t="n">
         <v>79225</v>
@@ -1725,17 +1722,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullemyr (Kullemyr), Dls</t>
+          <t>Kullemyr, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330443</v>
+        <v>330442</v>
       </c>
       <c r="R11" t="n">
-        <v>6532276</v>
+        <v>6532245</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1776,6 +1775,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Christine Bryngelsson, Oskar Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45416-2023 artfynd.xlsx
+++ b/artfynd/A 45416-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
